--- a/docs/部门工作日报-研发中心20260619.xlsx
+++ b/docs/部门工作日报-研发中心20260619.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Digital-transformation\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{901126A2-3819-4DA7-9AAD-210FFD176D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E81C64D2-AD38-49C4-84C8-A163D385D1CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3390" yWindow="645" windowWidth="21630" windowHeight="14835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="项目管理工作日报汇总" sheetId="5" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="15">
   <si>
     <t xml:space="preserve">部门工作日报 </t>
   </si>
@@ -55,72 +55,6 @@
     <t>协同事项</t>
   </si>
   <si>
-    <t>KRF26031重庆铁马-变速箱生产线改造项目</t>
-  </si>
-  <si>
-    <t>变速箱装配线工序节拍优化（完成100％）</t>
-  </si>
-  <si>
-    <t>郭鹏辉</t>
-  </si>
-  <si>
-    <t>修改变速箱装配线工序时序图</t>
-  </si>
-  <si>
-    <t>PPT中客户评审问题处理</t>
-  </si>
-  <si>
-    <t>李果</t>
-  </si>
-  <si>
-    <t>行星排组装自动化3D建模</t>
-  </si>
-  <si>
-    <t>杨照国</t>
-  </si>
-  <si>
-    <t>KRF25049井谷元-面饼预设备项目</t>
-  </si>
-  <si>
-    <t>KRF26001寓教于乐项目</t>
-  </si>
-  <si>
-    <t>弹射飞椅项目轨道细化100%</t>
-  </si>
-  <si>
-    <t>沈永华</t>
-  </si>
-  <si>
-    <t>弹射飞椅项目座椅机构细化50%</t>
-  </si>
-  <si>
-    <t>AI+数字化</t>
-  </si>
-  <si>
-    <t>确定办公应用的选择，制定后续方案及技术架构</t>
-  </si>
-  <si>
-    <t>周厚贵</t>
-  </si>
-  <si>
-    <t>售前-取纱芯设备项目</t>
-  </si>
-  <si>
-    <t>熟悉整体架构与业务流程</t>
-  </si>
-  <si>
-    <t>吴静一</t>
-  </si>
-  <si>
-    <t>售前-托盘自动生产线项目</t>
-  </si>
-  <si>
-    <t>内部会议详细讲解项目情况进行评审</t>
-  </si>
-  <si>
-    <t>符聪</t>
-  </si>
-  <si>
     <t>二、今日工作完成情况</t>
   </si>
   <si>
@@ -130,87 +64,18 @@
     <t>偏差分析及纠偏措施</t>
   </si>
   <si>
-    <t>项目方案设计工作计划</t>
-  </si>
-  <si>
-    <t>技术资料版本更新</t>
-  </si>
-  <si>
-    <t>行星排组装自动化3D建模20%</t>
-  </si>
-  <si>
-    <t>熟悉方案50%</t>
-  </si>
-  <si>
-    <t>方案预算</t>
-  </si>
-  <si>
-    <t>与客户确认流沙池项目平板及摄像头固定方式</t>
-  </si>
-  <si>
-    <t>对未完成结构进行设计</t>
-  </si>
-  <si>
-    <t>KRF25043金风-线缆预制设备项目</t>
-  </si>
-  <si>
-    <t>KRF25038分布式绿色能源系统</t>
-  </si>
-  <si>
-    <t>完成work Buddy和Qclaw接入钉钉，分别建立各自的钉钉机器人</t>
-  </si>
-  <si>
-    <t>陈芋如</t>
-  </si>
-  <si>
-    <t>初步对比二者的优劣点并输出对比表</t>
-  </si>
-  <si>
-    <t>完成WorkBuddy接入钉钉，进行简单的指令调试</t>
-  </si>
-  <si>
-    <t>初步学习C#语言，下载部分相关软件，配置环境</t>
-  </si>
-  <si>
-    <t>项目需求表评审未通过，补充关键信息</t>
-  </si>
-  <si>
-    <t>罗阳洋</t>
-  </si>
-  <si>
-    <t>项目需求表评审通过，提交营销中心</t>
-  </si>
-  <si>
-    <t>售前-仓储笼黑灯工厂项目</t>
-  </si>
-  <si>
-    <t>售前-智能折盒机项目</t>
-  </si>
-  <si>
-    <t>修改项目需求表，并提交制造中心</t>
-  </si>
-  <si>
-    <t>售前-托盘无损检测设备项目</t>
-  </si>
-  <si>
-    <t>项目需求表初版完成</t>
-  </si>
-  <si>
-    <t>尹志勇</t>
-  </si>
-  <si>
     <t>三、明日工作计划</t>
   </si>
   <si>
     <t>报告时间：2026.6.19</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -249,23 +114,6 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFC00000"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFC00000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -475,24 +323,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
@@ -504,15 +352,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -522,20 +364,47 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="6" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -551,60 +420,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -963,38 +778,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="31.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
     </row>
     <row r="2" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="19" t="s">
+      <c r="B2" s="25"/>
+      <c r="C2" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="19"/>
+      <c r="D2" s="26"/>
       <c r="E2" s="3"/>
-      <c r="F2" s="39" t="s">
-        <v>59</v>
+      <c r="F2" s="10" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="28.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
     </row>
     <row r="4" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
@@ -1017,162 +832,114 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="23">
+      <c r="A5" s="20">
         <v>1</v>
       </c>
-      <c r="B5" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
     </row>
     <row r="6" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="24"/>
-      <c r="B6" s="27"/>
-      <c r="C6" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="11"/>
+      <c r="A6" s="21"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="24"/>
-      <c r="B7" s="27"/>
-      <c r="C7" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="11"/>
+      <c r="A7" s="21"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="25"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="11"/>
+      <c r="A8" s="22"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="9"/>
     </row>
     <row r="9" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>2</v>
       </c>
-      <c r="B9" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="11"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="23">
+      <c r="A10" s="20">
         <v>3</v>
       </c>
-      <c r="B10" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="11"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="25"/>
-      <c r="B11" s="29"/>
-      <c r="C11" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="11"/>
+      <c r="A11" s="22"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="9"/>
     </row>
     <row r="12" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>4</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="10"/>
-      <c r="F12" s="11"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="9"/>
     </row>
     <row r="13" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="10">
+      <c r="A13" s="8">
         <v>5</v>
       </c>
-      <c r="B13" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="10"/>
-      <c r="F13" s="11"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="9"/>
     </row>
     <row r="14" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="10">
+      <c r="A14" s="8">
         <v>6</v>
       </c>
-      <c r="B14" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="11"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="9"/>
     </row>
     <row r="15" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="10"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="11"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="9"/>
     </row>
     <row r="16" spans="1:6" ht="28.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
+      <c r="A16" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="28"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
     </row>
     <row r="17" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
@@ -1185,346 +952,222 @@
         <v>6</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="23">
+      <c r="A18" s="20">
         <v>1</v>
       </c>
-      <c r="B18" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18" s="8">
-        <v>1</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F18" s="15"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
     </row>
     <row r="19" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="24"/>
-      <c r="B19" s="27"/>
-      <c r="C19" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D19" s="8">
-        <v>1</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F19" s="15"/>
+      <c r="A19" s="21"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
     </row>
     <row r="20" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="24"/>
-      <c r="B20" s="27"/>
-      <c r="C20" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" s="8">
-        <v>1</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="15"/>
+      <c r="A20" s="21"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
     </row>
     <row r="21" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="24"/>
-      <c r="B21" s="27"/>
-      <c r="C21" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="8">
-        <v>1</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="15"/>
+      <c r="A21" s="21"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
     </row>
     <row r="22" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="24"/>
-      <c r="B22" s="27"/>
-      <c r="C22" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D22" s="8">
-        <v>1</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F22" s="15"/>
+      <c r="A22" s="21"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
     </row>
     <row r="23" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="24"/>
-      <c r="B23" s="28"/>
-      <c r="C23" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D23" s="8">
-        <v>1</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" s="15"/>
+      <c r="A23" s="21"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
     </row>
     <row r="24" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="5">
         <v>2</v>
       </c>
-      <c r="B24" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C24" s="7"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="15"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
     </row>
     <row r="25" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="23">
+      <c r="A25" s="20">
         <v>3</v>
       </c>
-      <c r="B25" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D25" s="8">
-        <v>1</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F25" s="15"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
     </row>
     <row r="26" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="24"/>
-      <c r="B26" s="27"/>
-      <c r="C26" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D26" s="8">
-        <v>1</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="F26" s="15"/>
+      <c r="A26" s="21"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
     </row>
     <row r="27" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="24"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D27" s="8">
-        <v>1</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="F27" s="15"/>
+      <c r="A27" s="21"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
     </row>
     <row r="28" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="23">
+      <c r="A28" s="20">
         <v>4</v>
       </c>
-      <c r="B28" s="29" t="s">
-        <v>42</v>
-      </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="16"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
     </row>
     <row r="29" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="25"/>
-      <c r="B29" s="29"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="16"/>
+      <c r="A29" s="22"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
     </row>
     <row r="30" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="10">
+      <c r="A30" s="8">
         <v>5</v>
       </c>
-      <c r="B30" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" s="13"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="16"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
     </row>
     <row r="31" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="23">
+      <c r="A31" s="20">
         <v>6</v>
       </c>
-      <c r="B31" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D31" s="8">
-        <v>1</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="F31" s="16"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
     </row>
     <row r="32" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="24"/>
-      <c r="B32" s="29"/>
-      <c r="C32" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D32" s="8">
-        <v>1</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="F32" s="16"/>
+      <c r="A32" s="21"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
     </row>
     <row r="33" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="24"/>
-      <c r="B33" s="29"/>
-      <c r="C33" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D33" s="8">
-        <v>1</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="F33" s="16"/>
+      <c r="A33" s="21"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
     </row>
     <row r="34" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="25"/>
-      <c r="B34" s="29"/>
-      <c r="C34" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="D34" s="8">
-        <v>1</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="F34" s="16"/>
+      <c r="A34" s="22"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
     </row>
     <row r="35" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="10">
+      <c r="A35" s="8">
         <v>7</v>
       </c>
-      <c r="B35" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C35" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="D35" s="8">
-        <v>1</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="F35" s="16"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
     </row>
     <row r="36" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="10">
+      <c r="A36" s="8">
         <v>8</v>
       </c>
-      <c r="B36" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C36" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="D36" s="8">
-        <v>1</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F36" s="16"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
     </row>
     <row r="37" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="10">
+      <c r="A37" s="8">
         <v>9</v>
       </c>
-      <c r="B37" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="C37" s="13"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="16"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
     </row>
     <row r="38" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="10">
+      <c r="A38" s="8">
         <v>10</v>
       </c>
-      <c r="B38" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="D38" s="8">
-        <v>1</v>
-      </c>
-      <c r="E38" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="F38" s="16"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
     </row>
     <row r="39" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="10">
+      <c r="A39" s="8">
         <v>11</v>
       </c>
-      <c r="B39" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="C39" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="D39" s="8">
-        <v>1</v>
-      </c>
-      <c r="E39" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="F39" s="14"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
     </row>
     <row r="40" spans="1:6" ht="28.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="B40" s="22"/>
-      <c r="C40" s="22"/>
-      <c r="D40" s="22"/>
-      <c r="E40" s="22"/>
-      <c r="F40" s="22"/>
+      <c r="A40" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="B40" s="23"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="23"/>
     </row>
     <row r="41" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
@@ -1547,38 +1190,36 @@
       </c>
     </row>
     <row r="42" spans="1:6" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="23">
+      <c r="A42" s="20">
         <v>1</v>
       </c>
-      <c r="B42" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
     </row>
     <row r="43" spans="1:6" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="24"/>
-      <c r="B43" s="27"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="8"/>
+      <c r="A43" s="21"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
       <c r="E43" s="9"/>
       <c r="F43" s="9"/>
     </row>
     <row r="44" spans="1:6" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="24"/>
-      <c r="B44" s="27"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="8"/>
+      <c r="A44" s="21"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
       <c r="E44" s="9"/>
       <c r="F44" s="9"/>
     </row>
     <row r="45" spans="1:6" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="25"/>
-      <c r="B45" s="28"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="8"/>
+      <c r="A45" s="22"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
       <c r="E45" s="9"/>
       <c r="F45" s="9"/>
     </row>
@@ -1586,123 +1227,97 @@
       <c r="A46" s="5">
         <v>2</v>
       </c>
-      <c r="B46" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="12"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="11"/>
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="9"/>
     </row>
     <row r="47" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="23">
+      <c r="A47" s="20">
         <v>3</v>
       </c>
-      <c r="B47" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="C47" s="13"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="11"/>
+      <c r="B47" s="9"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="9"/>
+      <c r="F47" s="9"/>
     </row>
     <row r="48" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="25"/>
-      <c r="B48" s="29"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="11"/>
+      <c r="A48" s="22"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9"/>
     </row>
     <row r="49" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="5">
         <v>4</v>
       </c>
-      <c r="B49" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C49" s="7"/>
-      <c r="D49" s="10"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="11"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="9"/>
     </row>
     <row r="50" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="10">
+      <c r="A50" s="8">
         <v>5</v>
       </c>
-      <c r="B50" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C50" s="13"/>
-      <c r="D50" s="12"/>
-      <c r="E50" s="10"/>
-      <c r="F50" s="11"/>
+      <c r="B50" s="9"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="9"/>
+      <c r="F50" s="9"/>
     </row>
     <row r="51" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="10">
+      <c r="A51" s="8">
         <v>6</v>
       </c>
-      <c r="B51" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C51" s="7"/>
-      <c r="D51" s="12"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="11"/>
+      <c r="B51" s="9"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="9"/>
+      <c r="F51" s="9"/>
     </row>
     <row r="52" spans="1:6" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="10"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="10"/>
-      <c r="E52" s="10"/>
-      <c r="F52" s="11"/>
+      <c r="A52" s="8"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="9"/>
+      <c r="F52" s="9"/>
     </row>
     <row r="53" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="30"/>
-      <c r="B53" s="31"/>
-      <c r="C53" s="31"/>
-      <c r="D53" s="31"/>
-      <c r="E53" s="31"/>
-      <c r="F53" s="32"/>
+      <c r="A53" s="11"/>
+      <c r="B53" s="12"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="13"/>
     </row>
     <row r="54" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="33"/>
-      <c r="B54" s="34"/>
-      <c r="C54" s="34"/>
-      <c r="D54" s="34"/>
-      <c r="E54" s="34"/>
-      <c r="F54" s="35"/>
+      <c r="A54" s="14"/>
+      <c r="B54" s="15"/>
+      <c r="C54" s="15"/>
+      <c r="D54" s="15"/>
+      <c r="E54" s="15"/>
+      <c r="F54" s="16"/>
     </row>
     <row r="55" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="36"/>
-      <c r="B55" s="37"/>
-      <c r="C55" s="37"/>
-      <c r="D55" s="37"/>
-      <c r="E55" s="37"/>
-      <c r="F55" s="38"/>
+      <c r="A55" s="17"/>
+      <c r="B55" s="18"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="18"/>
+      <c r="F55" s="19"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B59"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="A53:F55"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B18:B23"/>
-    <mergeCell ref="B25:B27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="B31:B34"/>
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A18:A23"/>
-    <mergeCell ref="A25:A27"/>
+  <mergeCells count="15">
     <mergeCell ref="A28:A29"/>
     <mergeCell ref="A31:A34"/>
     <mergeCell ref="A1:F1"/>
@@ -1710,8 +1325,16 @@
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A53:F55"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A18:A23"/>
+    <mergeCell ref="A25:A27"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="C56">
     <cfRule type="iconSet" priority="5">
       <iconSet iconSet="3Flags">
